--- a/_ConfigExcels/Datas/__tables__.xlsx
+++ b/_ConfigExcels/Datas/__tables__.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -714,9 +714,44 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v>TbDisplayCase</v>
+      </c>
+      <c r="C10" t="str">
+        <v>DisplayCase</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>id</v>
+      </c>
+      <c r="F10" t="str">
+        <v>map</v>
+      </c>
+      <c r="G10" t="str">
+        <v>c</v>
+      </c>
+      <c r="H10" t="str">
+        <v>陈列柜配置表</v>
+      </c>
+      <c r="I10" t="str">
+        <v>display_case.xlsx</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/_ConfigExcels/Datas/__tables__.xlsx
+++ b/_ConfigExcels/Datas/__tables__.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -714,9 +714,114 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v/>
+      </c>
+      <c r="B10" t="str">
+        <v>TbDisplayCase</v>
+      </c>
+      <c r="C10" t="str">
+        <v>DisplayCase</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="str">
+        <v>id</v>
+      </c>
+      <c r="F10" t="str">
+        <v>map</v>
+      </c>
+      <c r="G10" t="str">
+        <v>c</v>
+      </c>
+      <c r="H10" t="str">
+        <v>陈列柜配置表</v>
+      </c>
+      <c r="I10" t="str">
+        <v>display_case.xlsx</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v/>
+      </c>
+      <c r="B11" t="str">
+        <v>TbShopBehavior</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ShopBehavior</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>one</v>
+      </c>
+      <c r="G11" t="str">
+        <v>c</v>
+      </c>
+      <c r="H11" t="str">
+        <v>街区行为全局参数</v>
+      </c>
+      <c r="I11" t="str">
+        <v>shop_behavior.xlsx</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v/>
+      </c>
+      <c r="B12" t="str">
+        <v>TbShopNpcProfile</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ShopNpcProfile</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="str">
+        <v>id</v>
+      </c>
+      <c r="F12" t="str">
+        <v>map</v>
+      </c>
+      <c r="G12" t="str">
+        <v>c</v>
+      </c>
+      <c r="H12" t="str">
+        <v>街区人物行为档案</v>
+      </c>
+      <c r="I12" t="str">
+        <v>shop_npc_profile.xlsx</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K12"/>
   </ignoredErrors>
 </worksheet>
 </file>